--- a/Data/PLC_address.xlsx
+++ b/Data/PLC_address.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syafiq_suhaimi\VSC projects\CMS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syafiq_suhaimi\VSC projects\CMS\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA980A2F-F47E-4224-B1D6-9B4A29471ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602621D7-3340-434A-85CD-8B63DC3594F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{94BA1258-89D2-475F-8625-7748BD6674CA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="185">
   <si>
     <t>Name</t>
   </si>
@@ -404,9 +404,6 @@
     <t>CP2E</t>
   </si>
   <si>
-    <t>Clock Constant</t>
-  </si>
-  <si>
     <t>H</t>
   </si>
   <si>
@@ -422,66 +419,6 @@
     <t>172.17.86.220</t>
   </si>
   <si>
-    <t>Ip M1</t>
-  </si>
-  <si>
-    <t>Ip M2</t>
-  </si>
-  <si>
-    <t>Ip M3</t>
-  </si>
-  <si>
-    <t>Ip M4</t>
-  </si>
-  <si>
-    <t>Ip M5</t>
-  </si>
-  <si>
-    <t>Ip M6</t>
-  </si>
-  <si>
-    <t>Ip M7</t>
-  </si>
-  <si>
-    <t>Ip M8</t>
-  </si>
-  <si>
-    <t>Ip M9</t>
-  </si>
-  <si>
-    <t>Ip M10</t>
-  </si>
-  <si>
-    <t>Ip M11</t>
-  </si>
-  <si>
-    <t>Ip M12</t>
-  </si>
-  <si>
-    <t>Ip M13</t>
-  </si>
-  <si>
-    <t>Ip M14</t>
-  </si>
-  <si>
-    <t>Ip M15</t>
-  </si>
-  <si>
-    <t>Ip M16</t>
-  </si>
-  <si>
-    <t>Ip M17</t>
-  </si>
-  <si>
-    <t>Ip M18</t>
-  </si>
-  <si>
-    <t>Ip M19</t>
-  </si>
-  <si>
-    <t>Ip M20</t>
-  </si>
-  <si>
     <t>0 CONSTANT</t>
   </si>
   <si>
@@ -515,24 +452,6 @@
     <t>Timer Function Block</t>
   </si>
   <si>
-    <t>Ip M21</t>
-  </si>
-  <si>
-    <t>Ip M22</t>
-  </si>
-  <si>
-    <t>Ip M23</t>
-  </si>
-  <si>
-    <t>Ip M24</t>
-  </si>
-  <si>
-    <t>Ip M25</t>
-  </si>
-  <si>
-    <t>Ip M26</t>
-  </si>
-  <si>
     <t>Change QC Signal</t>
   </si>
   <si>
@@ -639,6 +558,39 @@
   </si>
   <si>
     <t>HMI Stop Cat Color</t>
+  </si>
+  <si>
+    <t>Clock Constant Morning</t>
+  </si>
+  <si>
+    <t>Clock Constant Night</t>
+  </si>
+  <si>
+    <t>0 Constant</t>
+  </si>
+  <si>
+    <t>0.00 Constant</t>
+  </si>
+  <si>
+    <t>String Constant</t>
+  </si>
+  <si>
+    <t>Sub Node</t>
+  </si>
+  <si>
+    <t>Pass Prod</t>
+  </si>
+  <si>
+    <t>Pass Tech</t>
+  </si>
+  <si>
+    <t>Pass Main</t>
+  </si>
+  <si>
+    <t>Pass QC</t>
+  </si>
+  <si>
+    <t>Change Pass Signal</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +981,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1303,18 +1255,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1591,9 +1531,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1631,7 +1571,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1737,7 +1677,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1879,7 +1819,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2074,7 +2014,7 @@
         <v>45</v>
       </c>
       <c r="AD4" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:30" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2085,7 +2025,7 @@
       <c r="C5" s="17"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F5" s="18" t="str">
         <f>LEFT(E5,FIND("~",SUBSTITUTE(E5,".","~",LEN(E5)-LEN(SUBSTITUTE(E5,".",""))))-1) &amp; "." &amp; (VALUE(RIGHT(E5,LEN(E5)-FIND("~",SUBSTITUTE(E5,".","~",LEN(E5)-LEN(SUBSTITUTE(E5,".",""))))))+1)</f>
@@ -2424,7 +2364,7 @@
     </row>
     <row r="8" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="60" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8" s="61" t="s">
         <v>13</v>
@@ -2892,7 +2832,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="B12" s="61" t="s">
         <v>13</v>
@@ -6614,7 +6554,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3049BD40-9D77-4237-9F54-D8C44070C0CD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:L123"/>
+  <dimension ref="A2:L124"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.6328125" style="29" bestFit="1" customWidth="1"/>
@@ -6674,13 +6614,13 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="107" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="108" t="s">
+      <c r="A5" s="103" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="109" t="s">
+      <c r="C5" s="105" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="80" t="s">
@@ -6726,7 +6666,7 @@
       <c r="F6" s="28"/>
       <c r="G6" s="28"/>
       <c r="H6" s="29" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>13</v>
@@ -6739,15 +6679,13 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="105"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="28"/>
       <c r="G7" s="28"/>
       <c r="H7" s="29" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="I7" s="29" t="s">
         <v>13</v>
@@ -6778,7 +6716,7 @@
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
       <c r="H8" s="29" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="I8" s="29" t="s">
         <v>13</v>
@@ -6806,7 +6744,7 @@
       <c r="F9" s="28"/>
       <c r="G9" s="28"/>
       <c r="H9" s="29" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>14</v>
@@ -6907,7 +6845,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="39" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="B13" s="29" t="s">
         <v>13</v>
@@ -6921,7 +6859,7 @@
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
       <c r="H13" s="80" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I13" s="80" t="s">
         <v>16</v>
@@ -6941,7 +6879,7 @@
       <c r="F14" s="28"/>
       <c r="G14" s="28"/>
       <c r="H14" s="29" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="I14" s="29" t="s">
         <v>16</v>
@@ -6955,60 +6893,54 @@
       <c r="L14" s="28"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="28">
-        <v>70</v>
-      </c>
+      <c r="A15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="E15" s="28"/>
       <c r="F15" s="28"/>
       <c r="G15" s="28"/>
       <c r="H15" s="29" t="s">
-        <v>156</v>
+        <v>184</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>16</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="K15" s="28">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="K15" s="52">
+        <v>3.03</v>
       </c>
       <c r="L15" s="28"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="29" t="s">
+      <c r="A16" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="46" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="28">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F16" s="28"/>
       <c r="G16" s="28"/>
       <c r="H16" s="29" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="K16" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="28"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>14</v>
@@ -7017,57 +6949,64 @@
         <v>18</v>
       </c>
       <c r="E17" s="28">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F17" s="28"/>
       <c r="G17" s="28"/>
       <c r="H17" s="29" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="K17" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="28"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="47"/>
-      <c r="C18" s="48"/>
-      <c r="E18" s="28"/>
+      <c r="A18" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="28">
+        <v>90</v>
+      </c>
       <c r="F18" s="28"/>
       <c r="G18" s="28"/>
       <c r="H18" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="29" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K18" s="53">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="K18" s="28">
+        <v>2</v>
       </c>
       <c r="L18" s="28"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="28"/>
+      <c r="A19" s="47"/>
+      <c r="C19" s="48"/>
       <c r="E19" s="28"/>
       <c r="F19" s="28"/>
       <c r="G19" s="28"/>
       <c r="H19" s="29" t="s">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="I19" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K19" s="28">
-        <v>220</v>
+        <v>122</v>
+      </c>
+      <c r="K19" s="53">
+        <v>0</v>
       </c>
       <c r="L19" s="28"/>
     </row>
@@ -7077,16 +7016,16 @@
       <c r="F20" s="28"/>
       <c r="G20" s="28"/>
       <c r="H20" s="29" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K20" s="28">
-        <v>221</v>
+        <v>2</v>
       </c>
       <c r="L20" s="28"/>
     </row>
@@ -7096,157 +7035,147 @@
       <c r="F21" s="28"/>
       <c r="G21" s="28"/>
       <c r="H21" s="29" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K21" s="28">
-        <v>222</v>
+        <v>5</v>
       </c>
       <c r="L21" s="28"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C22" s="28"/>
+      <c r="E22" s="28"/>
       <c r="F22" s="28"/>
       <c r="G22" s="28"/>
       <c r="H22" s="29" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="I22" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K22" s="28">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="L22" s="28"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="79" t="s">
-        <v>102</v>
-      </c>
-      <c r="B23" s="80" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="80"/>
-      <c r="E23" s="82">
-        <v>110</v>
-      </c>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
       <c r="H23" s="29" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="I23" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K23" s="28">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="L23" s="28"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="B24" s="29" t="s">
+      <c r="A24" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="28">
-        <v>115</v>
+      <c r="D24" s="80"/>
+      <c r="E24" s="82">
+        <v>110</v>
       </c>
       <c r="F24" s="28"/>
       <c r="G24" s="28"/>
       <c r="H24" s="29" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K24" s="28">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="L24" s="28"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="79" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="80" t="s">
+      <c r="A25" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="80"/>
-      <c r="E25" s="82">
-        <v>120</v>
+      <c r="E25" s="28">
+        <v>115</v>
       </c>
       <c r="F25" s="28"/>
       <c r="G25" s="28"/>
       <c r="H25" s="29" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I25" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K25" s="28">
-        <v>226</v>
+        <v>25</v>
       </c>
       <c r="L25" s="28"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" s="29" t="s">
+      <c r="A26" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="28">
-        <v>125</v>
+      <c r="D26" s="80"/>
+      <c r="E26" s="82">
+        <v>120</v>
       </c>
       <c r="F26" s="28"/>
       <c r="G26" s="28"/>
       <c r="H26" s="29" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="I26" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K26" s="28">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="L26" s="28"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="39" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B27" s="29" t="s">
         <v>13</v>
@@ -7255,27 +7184,27 @@
         <v>18</v>
       </c>
       <c r="E27" s="28">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F27" s="28"/>
       <c r="G27" s="28"/>
       <c r="H27" s="29" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="I27" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K27" s="28">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="L27" s="28"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="39" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>13</v>
@@ -7284,41 +7213,50 @@
         <v>18</v>
       </c>
       <c r="E28" s="28">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
       <c r="H28" s="29" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K28" s="28">
-        <v>229</v>
+        <v>34</v>
       </c>
       <c r="L28" s="28"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="39"/>
-      <c r="C29" s="28"/>
-      <c r="E29" s="28"/>
+      <c r="A29" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="28">
+        <v>140</v>
+      </c>
       <c r="F29" s="28"/>
       <c r="G29" s="28"/>
       <c r="H29" s="29" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="I29" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K29" s="28">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="L29" s="28"/>
     </row>
@@ -7328,18 +7266,6 @@
       <c r="E30" s="28"/>
       <c r="F30" s="28"/>
       <c r="G30" s="28"/>
-      <c r="H30" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="I30" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K30" s="28">
-        <v>231</v>
-      </c>
       <c r="L30" s="28"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
@@ -7348,55 +7274,19 @@
       <c r="E31" s="28"/>
       <c r="F31" s="28"/>
       <c r="G31" s="28"/>
-      <c r="H31" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="I31" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K31" s="28">
-        <v>232</v>
-      </c>
       <c r="L31" s="28"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="41" t="s">
-        <v>200</v>
-      </c>
-      <c r="B32" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="43">
-        <v>180</v>
-      </c>
+      <c r="A32" s="39"/>
+      <c r="C32" s="28"/>
+      <c r="E32" s="28"/>
       <c r="F32" s="28"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K32" s="28">
-        <v>233</v>
-      </c>
       <c r="L32" s="28"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="41" t="s">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="B33" s="42" t="s">
         <v>13</v>
@@ -7408,59 +7298,35 @@
         <v>115</v>
       </c>
       <c r="E33" s="43">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F33" s="28"/>
       <c r="G33" s="28"/>
-      <c r="H33" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="I33" s="29" t="s">
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A34" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="J33" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K33" s="28">
-        <v>234</v>
-      </c>
-      <c r="L33" s="28"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="79" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="81" t="s">
+      <c r="C34" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="80" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="82">
-        <v>200</v>
+      <c r="D34" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="43">
+        <v>190</v>
       </c>
       <c r="F34" s="28"/>
       <c r="G34" s="28"/>
-      <c r="H34" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I34" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K34" s="28">
-        <v>235</v>
-      </c>
       <c r="L34" s="28"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35" s="80" t="s">
         <v>15</v>
@@ -7472,62 +7338,38 @@
         <v>50</v>
       </c>
       <c r="E35" s="82">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F35" s="28"/>
       <c r="G35" s="28"/>
-      <c r="H35" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="I35" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K35" s="28">
-        <v>236</v>
-      </c>
       <c r="L35" s="28"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="42" t="s">
+      <c r="A36" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="43" t="s">
+      <c r="C36" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" s="43">
-        <v>400</v>
+      <c r="D36" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="82">
+        <v>300</v>
       </c>
       <c r="F36" s="28"/>
       <c r="G36" s="28"/>
-      <c r="H36" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="I36" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K36" s="28">
-        <v>237</v>
-      </c>
       <c r="L36" s="28"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="41" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B37" s="42" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C37" s="43" t="s">
         <v>18</v>
@@ -7536,261 +7378,165 @@
         <v>115</v>
       </c>
       <c r="E37" s="43">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F37" s="28"/>
       <c r="G37" s="28"/>
-      <c r="H37" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="I37" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K37" s="28">
-        <v>238</v>
-      </c>
       <c r="L37" s="28"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="D38" s="45"/>
-      <c r="E38" s="46">
-        <v>0</v>
+      <c r="A38" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="43">
+        <v>500</v>
       </c>
       <c r="F38" s="28"/>
       <c r="G38" s="28"/>
-      <c r="H38" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="I38" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K38" s="28">
-        <v>239</v>
-      </c>
       <c r="L38" s="28"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="B39" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="48">
-        <v>5</v>
+      <c r="A39" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="45"/>
+      <c r="E39" s="46">
+        <v>0</v>
       </c>
       <c r="F39" s="28"/>
       <c r="G39" s="28"/>
-      <c r="H39" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I39" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K39" s="28">
-        <v>240</v>
-      </c>
       <c r="L39" s="28"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="47" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="B40" s="29" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E40" s="48">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F40" s="28"/>
       <c r="G40" s="28"/>
-      <c r="H40" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="I40" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K40" s="28">
-        <v>241</v>
-      </c>
       <c r="L40" s="28"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="47" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E41" s="48">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F41" s="28"/>
       <c r="G41" s="28"/>
-      <c r="H41" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="I41" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K41" s="28">
-        <v>242</v>
-      </c>
       <c r="L41" s="28"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="B42" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="51">
-        <v>20</v>
+      <c r="A42" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="48">
+        <v>15</v>
       </c>
       <c r="F42" s="28"/>
       <c r="G42" s="28"/>
-      <c r="H42" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="I42" s="29" t="s">
+      <c r="L42" s="28"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="J42" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K42" s="28">
-        <v>243</v>
-      </c>
-      <c r="L42" s="28"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="47" t="s">
-        <v>196</v>
-      </c>
-      <c r="B43" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" s="28">
-        <v>30</v>
+      <c r="C43" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="50"/>
+      <c r="E43" s="51">
+        <v>20</v>
       </c>
       <c r="F43" s="28"/>
       <c r="G43" s="28"/>
-      <c r="H43" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="I43" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K43" s="28">
-        <v>244</v>
-      </c>
       <c r="L43" s="28"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="47" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="B44" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E44" s="28">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F44" s="28"/>
       <c r="G44" s="28"/>
-      <c r="H44" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="I44" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K44" s="28">
-        <v>245</v>
-      </c>
       <c r="L44" s="28"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="47" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="B45" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E45" s="28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F45" s="28"/>
       <c r="G45" s="28"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
       <c r="L45" s="28"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="83" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="80" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="84" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="80"/>
-      <c r="E46" s="82">
-        <v>740</v>
+      <c r="A46" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E46" s="28">
+        <v>34</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" s="28"/>
@@ -7800,7 +7546,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B47" s="80" t="s">
         <v>14</v>
@@ -7810,7 +7556,7 @@
       </c>
       <c r="D47" s="80"/>
       <c r="E47" s="82">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" s="28"/>
@@ -7820,7 +7566,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="83" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B48" s="80" t="s">
         <v>14</v>
@@ -7830,7 +7576,7 @@
       </c>
       <c r="D48" s="80"/>
       <c r="E48" s="82">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="F48" s="28"/>
       <c r="G48" s="28"/>
@@ -7840,7 +7586,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B49" s="80" t="s">
         <v>14</v>
@@ -7850,7 +7596,7 @@
       </c>
       <c r="D49" s="80"/>
       <c r="E49" s="82">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
@@ -7860,7 +7606,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="83" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B50" s="80" t="s">
         <v>14</v>
@@ -7870,7 +7616,7 @@
       </c>
       <c r="D50" s="80"/>
       <c r="E50" s="82">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="F50" s="28"/>
       <c r="G50" s="28"/>
@@ -7880,7 +7626,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="83" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B51" s="80" t="s">
         <v>14</v>
@@ -7890,15 +7636,17 @@
       </c>
       <c r="D51" s="80"/>
       <c r="E51" s="82">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="F51" s="28"/>
       <c r="G51" s="28"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
       <c r="L51" s="28"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="83" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B52" s="80" t="s">
         <v>14</v>
@@ -7908,7 +7656,7 @@
       </c>
       <c r="D52" s="80"/>
       <c r="E52" s="82">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="F52" s="28"/>
       <c r="G52" s="28"/>
@@ -7916,7 +7664,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="83" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B53" s="80" t="s">
         <v>14</v>
@@ -7926,16 +7674,26 @@
       </c>
       <c r="D53" s="80"/>
       <c r="E53" s="82">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="F53" s="28"/>
       <c r="G53" s="28"/>
       <c r="L53" s="28"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" s="47"/>
-      <c r="C54" s="48"/>
-      <c r="E54" s="28"/>
+      <c r="A54" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="80"/>
+      <c r="E54" s="82">
+        <v>775</v>
+      </c>
       <c r="F54" s="28"/>
       <c r="G54" s="28"/>
       <c r="L54" s="28"/>
@@ -7949,34 +7707,25 @@
       <c r="L55" s="28"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56" s="49"/>
-      <c r="B56" s="50"/>
-      <c r="C56" s="51"/>
+      <c r="A56" s="47"/>
+      <c r="C56" s="48"/>
       <c r="E56" s="28"/>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
       <c r="L56" s="28"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="B57" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C57" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" s="28">
-        <v>700</v>
-      </c>
+      <c r="A57" s="49"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="51"/>
+      <c r="E57" s="28"/>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
       <c r="L57" s="28"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B58" s="29" t="s">
         <v>14</v>
@@ -7985,7 +7734,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="28">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="F58" s="28"/>
       <c r="G58" s="28"/>
@@ -7993,7 +7742,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B59" s="29" t="s">
         <v>14</v>
@@ -8002,7 +7751,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="28">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
@@ -8010,7 +7759,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B60" s="29" t="s">
         <v>14</v>
@@ -8019,7 +7768,7 @@
         <v>18</v>
       </c>
       <c r="E60" s="28">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
@@ -8027,7 +7776,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B61" s="29" t="s">
         <v>14</v>
@@ -8036,7 +7785,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="28">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
@@ -8044,7 +7793,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B62" s="29" t="s">
         <v>14</v>
@@ -8053,7 +7802,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="28">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
@@ -8061,7 +7810,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" s="29" t="s">
         <v>14</v>
@@ -8070,7 +7819,7 @@
         <v>18</v>
       </c>
       <c r="E63" s="28">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
@@ -8078,7 +7827,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B64" s="29" t="s">
         <v>14</v>
@@ -8087,16 +7836,25 @@
         <v>18</v>
       </c>
       <c r="E64" s="28">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="F64" s="28"/>
       <c r="G64" s="28"/>
       <c r="L64" s="28"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A65" s="47"/>
-      <c r="C65" s="48"/>
-      <c r="E65" s="28"/>
+      <c r="A65" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="28">
+        <v>735</v>
+      </c>
       <c r="F65" s="28"/>
       <c r="G65" s="28"/>
       <c r="L65" s="28"/>
@@ -8118,103 +7876,90 @@
       <c r="L67" s="28"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A68" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="B68" s="80" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="84" t="s">
-        <v>18</v>
-      </c>
-      <c r="D68" s="80" t="s">
-        <v>50</v>
-      </c>
-      <c r="E68" s="82">
-        <v>1000</v>
-      </c>
+      <c r="A68" s="47"/>
+      <c r="C68" s="48"/>
+      <c r="E68" s="28"/>
       <c r="F68" s="28"/>
       <c r="G68" s="28"/>
       <c r="L68" s="28"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A69" s="44" t="s">
+      <c r="A69" s="83" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69" s="82">
+        <v>1000</v>
+      </c>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="L69" s="28"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A70" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="B69" s="45" t="s">
+      <c r="B70" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C69" s="46" t="s">
+      <c r="C70" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="52">
+      <c r="E70" s="52">
         <v>0</v>
-      </c>
-      <c r="F69" s="52"/>
-      <c r="G69" s="52"/>
-      <c r="L69" s="52"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A70" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="B70" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E70" s="52">
-        <v>1</v>
       </c>
       <c r="F70" s="52"/>
       <c r="G70" s="52"/>
       <c r="L70" s="52"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A71" s="97" t="s">
-        <v>96</v>
-      </c>
-      <c r="B71" s="42" t="s">
+      <c r="A71" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C71" s="98" t="s">
+      <c r="C71" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D71" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E71" s="99">
-        <v>2</v>
+      <c r="E71" s="52">
+        <v>1</v>
       </c>
       <c r="F71" s="52"/>
       <c r="G71" s="52"/>
       <c r="L71" s="52"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A72" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="B72" s="29" t="s">
+      <c r="A72" s="97" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="48" t="s">
+      <c r="C72" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="E72" s="52">
-        <v>3</v>
+      <c r="D72" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E72" s="99">
+        <v>2</v>
       </c>
       <c r="F72" s="52"/>
       <c r="G72" s="52"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="52"/>
-      <c r="J72" s="52"/>
-      <c r="K72" s="52"/>
       <c r="L72" s="52"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="47" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="B73" s="29" t="s">
         <v>16</v>
@@ -8223,7 +7968,7 @@
         <v>19</v>
       </c>
       <c r="E73" s="52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F73" s="52"/>
       <c r="G73" s="52"/>
@@ -8234,20 +7979,17 @@
       <c r="L73" s="52"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A74" s="83" t="s">
-        <v>106</v>
-      </c>
-      <c r="B74" s="80" t="s">
+      <c r="A74" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="84" t="s">
+      <c r="C74" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D74" s="80" t="s">
-        <v>50</v>
-      </c>
-      <c r="E74" s="85">
-        <v>5</v>
+      <c r="E74" s="52">
+        <v>4</v>
       </c>
       <c r="F74" s="52"/>
       <c r="G74" s="52"/>
@@ -8258,20 +8000,20 @@
       <c r="L74" s="52"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A75" s="97" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75" s="42" t="s">
+      <c r="A75" s="83" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="98" t="s">
+      <c r="C75" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D75" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E75" s="99">
-        <v>6</v>
+      <c r="D75" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E75" s="85">
+        <v>5</v>
       </c>
       <c r="F75" s="52"/>
       <c r="G75" s="52"/>
@@ -8282,20 +8024,20 @@
       <c r="L75" s="52"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A76" s="100" t="s">
-        <v>119</v>
-      </c>
-      <c r="B76" s="101" t="s">
+      <c r="A76" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B76" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="102" t="s">
+      <c r="C76" s="98" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="42" t="s">
         <v>115</v>
       </c>
       <c r="E76" s="99">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F76" s="52"/>
       <c r="G76" s="52"/>
@@ -8306,20 +8048,20 @@
       <c r="L76" s="52"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A77" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" s="42" t="s">
+      <c r="A77" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="C77" s="98" t="s">
+      <c r="C77" s="102" t="s">
         <v>19</v>
       </c>
       <c r="D77" s="42" t="s">
         <v>115</v>
       </c>
       <c r="E77" s="99">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F77" s="52"/>
       <c r="G77" s="52"/>
@@ -8331,7 +8073,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="97" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="B78" s="42" t="s">
         <v>16</v>
@@ -8343,7 +8085,7 @@
         <v>115</v>
       </c>
       <c r="E78" s="99">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F78" s="52"/>
       <c r="G78" s="52"/>
@@ -8354,20 +8096,20 @@
       <c r="L78" s="52"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A79" s="83" t="s">
-        <v>155</v>
-      </c>
-      <c r="B79" s="80" t="s">
+      <c r="A79" s="97" t="s">
+        <v>133</v>
+      </c>
+      <c r="B79" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="84" t="s">
+      <c r="C79" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="D79" s="80" t="s">
-        <v>50</v>
-      </c>
-      <c r="E79" s="85">
-        <v>10</v>
+      <c r="D79" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E79" s="99">
+        <v>9</v>
       </c>
       <c r="F79" s="52"/>
       <c r="G79" s="52"/>
@@ -8379,7 +8121,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="83" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="B80" s="80" t="s">
         <v>16</v>
@@ -8387,9 +8129,11 @@
       <c r="C80" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D80" s="80"/>
+      <c r="D80" s="80" t="s">
+        <v>50</v>
+      </c>
       <c r="E80" s="85">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F80" s="52"/>
       <c r="G80" s="52"/>
@@ -8401,7 +8145,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="83" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B81" s="80" t="s">
         <v>16</v>
@@ -8411,7 +8155,7 @@
       </c>
       <c r="D81" s="80"/>
       <c r="E81" s="85">
-        <v>20.010000000000002</v>
+        <v>20</v>
       </c>
       <c r="F81" s="52"/>
       <c r="G81" s="52"/>
@@ -8423,7 +8167,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="83" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="B82" s="80" t="s">
         <v>16</v>
@@ -8433,7 +8177,7 @@
       </c>
       <c r="D82" s="80"/>
       <c r="E82" s="85">
-        <v>20.02</v>
+        <v>20.010000000000002</v>
       </c>
       <c r="F82" s="52"/>
       <c r="G82" s="52"/>
@@ -8445,7 +8189,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="83" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B83" s="80" t="s">
         <v>16</v>
@@ -8455,7 +8199,7 @@
       </c>
       <c r="D83" s="80"/>
       <c r="E83" s="85">
-        <v>20.03</v>
+        <v>20.02</v>
       </c>
       <c r="F83" s="52"/>
       <c r="G83" s="52"/>
@@ -8467,7 +8211,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="83" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="B84" s="80" t="s">
         <v>16</v>
@@ -8477,7 +8221,7 @@
       </c>
       <c r="D84" s="80"/>
       <c r="E84" s="85">
-        <v>20.05</v>
+        <v>20.03</v>
       </c>
       <c r="F84" s="52"/>
       <c r="G84" s="52"/>
@@ -8489,7 +8233,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="83" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="B85" s="80" t="s">
         <v>16</v>
@@ -8499,7 +8243,7 @@
       </c>
       <c r="D85" s="80"/>
       <c r="E85" s="85">
-        <v>20.059999999999999</v>
+        <v>20.05</v>
       </c>
       <c r="F85" s="52"/>
       <c r="G85" s="52"/>
@@ -8510,20 +8254,18 @@
       <c r="L85" s="52"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A86" s="97" t="s">
-        <v>173</v>
-      </c>
-      <c r="B86" s="42" t="s">
+      <c r="A86" s="83" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C86" s="98" t="s">
+      <c r="C86" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D86" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E86" s="99">
-        <v>30</v>
+      <c r="D86" s="80"/>
+      <c r="E86" s="85">
+        <v>20.059999999999999</v>
       </c>
       <c r="F86" s="52"/>
       <c r="G86" s="52"/>
@@ -8534,9 +8276,21 @@
       <c r="L86" s="52"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A87" s="47"/>
-      <c r="C87" s="48"/>
-      <c r="E87" s="52"/>
+      <c r="A87" s="97" t="s">
+        <v>146</v>
+      </c>
+      <c r="B87" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E87" s="99">
+        <v>30</v>
+      </c>
       <c r="F87" s="52"/>
       <c r="G87" s="52"/>
       <c r="H87" s="52"/>
@@ -8606,18 +8360,9 @@
       <c r="L92" s="52"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A93" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="B93" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="52">
-        <v>60</v>
-      </c>
+      <c r="A93" s="47"/>
+      <c r="C93" s="48"/>
+      <c r="E93" s="52"/>
       <c r="F93" s="52"/>
       <c r="G93" s="52"/>
       <c r="H93" s="52"/>
@@ -8627,17 +8372,17 @@
       <c r="L93" s="52"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A94" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="B94" s="29" t="s">
+      <c r="A94" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C94" s="48" t="s">
+      <c r="C94" s="46" t="s">
         <v>19</v>
       </c>
       <c r="E94" s="52">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F94" s="52"/>
       <c r="G94" s="52"/>
@@ -8649,7 +8394,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B95" s="29" t="s">
         <v>16</v>
@@ -8658,7 +8403,7 @@
         <v>19</v>
       </c>
       <c r="E95" s="52">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F95" s="52"/>
       <c r="G95" s="52"/>
@@ -8670,7 +8415,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="47" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B96" s="29" t="s">
         <v>16</v>
@@ -8679,7 +8424,7 @@
         <v>19</v>
       </c>
       <c r="E96" s="52">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F96" s="52"/>
       <c r="G96" s="52"/>
@@ -8691,16 +8436,16 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="47" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B97" s="29" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="C97" s="48" t="s">
         <v>19</v>
       </c>
       <c r="E97" s="52">
-        <v>63.01</v>
+        <v>63</v>
       </c>
       <c r="F97" s="52"/>
       <c r="G97" s="52"/>
@@ -8712,16 +8457,16 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B98" s="29" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="C98" s="48" t="s">
         <v>19</v>
       </c>
       <c r="E98" s="52">
-        <v>64</v>
+        <v>63.01</v>
       </c>
       <c r="F98" s="52"/>
       <c r="G98" s="52"/>
@@ -8732,17 +8477,17 @@
       <c r="L98" s="52"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A99" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="B99" s="50" t="s">
+      <c r="A99" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B99" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C99" s="51" t="s">
+      <c r="C99" s="48" t="s">
         <v>19</v>
       </c>
       <c r="E99" s="52">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F99" s="52"/>
       <c r="G99" s="52"/>
@@ -8753,8 +8498,18 @@
       <c r="L99" s="52"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C100" s="48"/>
-      <c r="E100" s="52"/>
+      <c r="A100" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B100" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" s="52">
+        <v>65</v>
+      </c>
       <c r="F100" s="52"/>
       <c r="G100" s="52"/>
       <c r="H100" s="52"/>
@@ -8764,7 +8519,6 @@
       <c r="L100" s="52"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A101" s="47"/>
       <c r="C101" s="48"/>
       <c r="E101" s="52"/>
       <c r="F101" s="52"/>
@@ -8776,9 +8530,8 @@
       <c r="L101" s="52"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A102" s="49"/>
-      <c r="B102" s="50"/>
-      <c r="C102" s="51"/>
+      <c r="A102" s="47"/>
+      <c r="C102" s="48"/>
       <c r="E102" s="52"/>
       <c r="F102" s="52"/>
       <c r="G102" s="52"/>
@@ -8789,18 +8542,10 @@
       <c r="L102" s="52"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A103" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B103" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="52">
-        <v>70</v>
-      </c>
+      <c r="A103" s="49"/>
+      <c r="B103" s="50"/>
+      <c r="C103" s="51"/>
+      <c r="E103" s="52"/>
       <c r="F103" s="52"/>
       <c r="G103" s="52"/>
       <c r="H103" s="52"/>
@@ -8810,17 +8555,17 @@
       <c r="L103" s="52"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A104" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="B104" s="29" t="s">
+      <c r="A104" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B104" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C104" s="48" t="s">
+      <c r="C104" s="46" t="s">
         <v>19</v>
       </c>
       <c r="E104" s="52">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F104" s="52"/>
       <c r="G104" s="52"/>
@@ -8832,7 +8577,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B105" s="29" t="s">
         <v>16</v>
@@ -8841,7 +8586,7 @@
         <v>19</v>
       </c>
       <c r="E105" s="52">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F105" s="52"/>
       <c r="G105" s="52"/>
@@ -8853,7 +8598,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B106" s="29" t="s">
         <v>16</v>
@@ -8862,7 +8607,7 @@
         <v>19</v>
       </c>
       <c r="E106" s="52">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F106" s="52"/>
       <c r="G106" s="52"/>
@@ -8874,7 +8619,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B107" s="29" t="s">
         <v>16</v>
@@ -8883,7 +8628,7 @@
         <v>19</v>
       </c>
       <c r="E107" s="52">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F107" s="52"/>
       <c r="G107" s="52"/>
@@ -8895,7 +8640,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B108" s="29" t="s">
         <v>16</v>
@@ -8904,7 +8649,7 @@
         <v>19</v>
       </c>
       <c r="E108" s="52">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F108" s="52"/>
       <c r="G108" s="52"/>
@@ -8916,7 +8661,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="47" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B109" s="29" t="s">
         <v>16</v>
@@ -8925,7 +8670,7 @@
         <v>19</v>
       </c>
       <c r="E109" s="52">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F109" s="52"/>
       <c r="G109" s="52"/>
@@ -8936,17 +8681,17 @@
       <c r="L109" s="52"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A110" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="B110" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="C110" s="51" t="s">
+      <c r="A110" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" s="48" t="s">
         <v>19</v>
       </c>
       <c r="E110" s="52">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F110" s="52"/>
       <c r="G110" s="52"/>
@@ -8957,9 +8702,18 @@
       <c r="L110" s="52"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A111" s="47"/>
-      <c r="C111" s="48"/>
-      <c r="E111" s="52"/>
+      <c r="A111" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C111" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="52">
+        <v>77</v>
+      </c>
       <c r="F111" s="52"/>
       <c r="G111" s="52"/>
       <c r="H111" s="52"/>
@@ -8969,9 +8723,8 @@
       <c r="L111" s="52"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A112" s="49"/>
-      <c r="B112" s="50"/>
-      <c r="C112" s="51"/>
+      <c r="A112" s="47"/>
+      <c r="C112" s="48"/>
       <c r="E112" s="52"/>
       <c r="F112" s="52"/>
       <c r="G112" s="52"/>
@@ -8982,18 +8735,10 @@
       <c r="L112" s="52"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A113" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B113" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="E113" s="52">
-        <v>0</v>
-      </c>
+      <c r="A113" s="49"/>
+      <c r="B113" s="50"/>
+      <c r="C113" s="51"/>
+      <c r="E113" s="52"/>
       <c r="F113" s="52"/>
       <c r="G113" s="52"/>
       <c r="H113" s="52"/>
@@ -9003,17 +8748,17 @@
       <c r="L113" s="52"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A114" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B114" s="29" t="s">
+      <c r="A114" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B114" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C114" s="48" t="s">
+      <c r="C114" s="46" t="s">
         <v>51</v>
       </c>
       <c r="E114" s="52">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F114" s="52"/>
       <c r="G114" s="52"/>
@@ -9025,7 +8770,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B115" s="29" t="s">
         <v>16</v>
@@ -9034,7 +8779,7 @@
         <v>51</v>
       </c>
       <c r="E115" s="52">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="52"/>
@@ -9046,7 +8791,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B116" s="29" t="s">
         <v>16</v>
@@ -9055,7 +8800,7 @@
         <v>51</v>
       </c>
       <c r="E116" s="52">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F116" s="52"/>
       <c r="G116" s="52"/>
@@ -9067,7 +8812,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B117" s="29" t="s">
         <v>16</v>
@@ -9076,7 +8821,7 @@
         <v>51</v>
       </c>
       <c r="E117" s="52">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F117" s="52"/>
       <c r="G117" s="52"/>
@@ -9088,7 +8833,7 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B118" s="29" t="s">
         <v>16</v>
@@ -9097,7 +8842,7 @@
         <v>51</v>
       </c>
       <c r="E118" s="52">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F118" s="52"/>
       <c r="G118" s="52"/>
@@ -9109,7 +8854,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B119" s="29" t="s">
         <v>16</v>
@@ -9118,7 +8863,7 @@
         <v>51</v>
       </c>
       <c r="E119" s="52">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F119" s="52"/>
       <c r="G119" s="52"/>
@@ -9130,7 +8875,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B120" s="29" t="s">
         <v>16</v>
@@ -9139,7 +8884,7 @@
         <v>51</v>
       </c>
       <c r="E120" s="52">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="F120" s="52"/>
       <c r="G120" s="52"/>
@@ -9151,7 +8896,7 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B121" s="29" t="s">
         <v>16</v>
@@ -9160,7 +8905,7 @@
         <v>51</v>
       </c>
       <c r="E121" s="52">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F121" s="52"/>
       <c r="G121" s="52"/>
@@ -9171,17 +8916,17 @@
       <c r="L121" s="52"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A122" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="B122" s="50" t="s">
+      <c r="A122" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B122" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C122" s="51" t="s">
-        <v>52</v>
+      <c r="C122" s="48" t="s">
+        <v>51</v>
       </c>
       <c r="E122" s="52">
-        <v>100</v>
+        <v>0.08</v>
       </c>
       <c r="F122" s="52"/>
       <c r="G122" s="52"/>
@@ -9192,9 +8937,30 @@
       <c r="L122" s="52"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A123" s="47"/>
-      <c r="C123" s="48"/>
-      <c r="E123" s="53"/>
+      <c r="A123" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B123" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="E123" s="52">
+        <v>100</v>
+      </c>
+      <c r="F123" s="52"/>
+      <c r="G123" s="52"/>
+      <c r="H123" s="52"/>
+      <c r="I123" s="52"/>
+      <c r="J123" s="52"/>
+      <c r="K123" s="52"/>
+      <c r="L123" s="52"/>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A124" s="47"/>
+      <c r="C124" s="48"/>
+      <c r="E124" s="53"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9217,23 +8983,23 @@
   <sheetData>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F4" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="92" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="C5" s="92" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D5" s="91" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="93" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="C6" s="95" t="s">
         <v>51</v>
@@ -9244,7 +9010,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="93" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="C7" s="95" t="s">
         <v>51</v>
@@ -9255,7 +9021,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="93" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="C8" s="95" t="s">
         <v>51</v>
@@ -9277,7 +9043,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="93" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="C10" s="95" t="s">
         <v>51</v>
@@ -9288,7 +9054,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="93" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="C11" s="95" t="s">
         <v>51</v>
@@ -9297,12 +9063,12 @@
         <v>0.05</v>
       </c>
       <c r="F11" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="93" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="C12" s="95" t="s">
         <v>51</v>
@@ -9313,7 +9079,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="93" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="C13" s="95" t="s">
         <v>51</v>
@@ -9324,7 +9090,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="93" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="C14" s="95" t="s">
         <v>51</v>
@@ -9335,7 +9101,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="94" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="C15" s="96" t="s">
         <v>52</v>
